--- a/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
@@ -28,7 +28,7 @@
     <t>초등 고학년 용돈기입장</t>
   </si>
   <si>
-    <t>“섬 여행을 꿈꾸며 모으는 용돈”</t>
+    <t>“친구에게 빌린 돈은 꼭 적어요”</t>
   </si>
   <si>
     <t>섬마을 선착장 테마</t>

--- a/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
@@ -23,12 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="45">
   <si>
     <t>초등 고학년 용돈기입장</t>
-  </si>
-  <si>
-    <t>“친구에게 빌린 돈은 꼭 적어요”</t>
   </si>
   <si>
     <t>섬마을 선착장 테마</t>
@@ -1369,65 +1366,63 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="32" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="8"/>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="9"/>
     </row>
@@ -1470,21 +1465,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="12">
         <v>2026</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="14">
         <v>0</v>
@@ -1496,22 +1489,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1519,7 +1512,7 @@
         <v>46023</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="18">
@@ -1536,10 +1529,10 @@
         <v>46027</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18">
@@ -1555,10 +1548,10 @@
         <v>46034</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18">
@@ -1574,10 +1567,10 @@
         <v>46041</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18">
@@ -1593,7 +1586,7 @@
         <v>46054</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="18">
@@ -1610,10 +1603,10 @@
         <v>46058</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18">
@@ -1629,10 +1622,10 @@
         <v>46065</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18">
@@ -1648,10 +1641,10 @@
         <v>46072</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18">
@@ -1667,7 +1660,7 @@
         <v>46082</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="18">
@@ -1684,10 +1677,10 @@
         <v>46086</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18">
@@ -1703,10 +1696,10 @@
         <v>46093</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18">
@@ -1722,10 +1715,10 @@
         <v>46100</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18">
@@ -1741,7 +1734,7 @@
         <v>46113</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18">
@@ -1758,10 +1751,10 @@
         <v>46117</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18">
@@ -1777,10 +1770,10 @@
         <v>46124</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18">
@@ -1796,10 +1789,10 @@
         <v>46131</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18">
@@ -1815,7 +1808,7 @@
         <v>46143</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18">
@@ -1832,10 +1825,10 @@
         <v>46147</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18">
@@ -1851,10 +1844,10 @@
         <v>46154</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18">
@@ -1870,10 +1863,10 @@
         <v>46161</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="18">
@@ -1889,7 +1882,7 @@
         <v>46174</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="18">
@@ -1906,10 +1899,10 @@
         <v>46178</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="18">
@@ -1925,10 +1918,10 @@
         <v>46185</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="18">
@@ -1944,10 +1937,10 @@
         <v>46192</v>
       </c>
       <c r="B29" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="18">
@@ -5038,7 +5031,7 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -5050,22 +5043,22 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -5085,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H5)</f>
@@ -5109,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H6)</f>
@@ -5133,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H7)</f>
@@ -5157,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H8)</f>
@@ -5181,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H9)</f>
@@ -5205,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H10)</f>
@@ -5229,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H11)</f>
@@ -5253,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="25">
         <f>SUM(I5:I11)</f>
@@ -5330,7 +5323,7 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="26">
         <f>SUM(C5:C16)</f>
@@ -5371,21 +5364,21 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1" s="20"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>37</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="14">
         <v>120000</v>
@@ -5393,7 +5386,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="29">
         <f>StartBal+SUM('기입장'!$D$6:$D$305)-SUM('기입장'!$E$6:$E$305)+SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,"저금")</f>
@@ -5402,7 +5395,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="30">
         <f>IF(C4=0,0,C6/C4)</f>
@@ -5411,7 +5404,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="29">
         <f>MAX(0,C4-C6)</f>
@@ -5420,7 +5413,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(AVERAGEIF('월요약'!$E$5:$E$16,"&lt;&gt;0"),0)</f>
@@ -5429,7 +5422,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="31">
         <f>IF(C9&lt;=0,"-",IF(C8=0,"달성!",ROUNDUP(C8/C9,0)&amp;"개월"))</f>
@@ -5438,7 +5431,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8"/>
     </row>

--- a/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_22_초등고학년_섬마을선착장.xlsx
@@ -61,7 +61,7 @@
     <t>처음 들어 있는 줄은 예시예요. 지우고 내 용돈으로 바꿔 쓰세요.</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>기준 연도</t>
@@ -164,13 +164,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="0&quot;월&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0"/>
-    <numFmt numFmtId="168" formatCode="0%"/>
-    <numFmt numFmtId="169" formatCode="@"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="&quot;올해&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="167" formatCode="0&quot;월&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -388,16 +389,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -406,19 +407,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -427,10 +428,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,13 +440,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
